--- a/data_extactor/batch_10_fa/trimmed/batch_0003_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0003_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نظارت | یادگیری فعال | نگارش | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | نگارش | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | مدیریت و امور اداری | پرسنلی و منابع انسانی | ایمنی و امنیت عمومی | شیمی</t>
+          <t>مکانیک | مهندسی و فناوری | تولید و فرآوری | مدیریت و اداره | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | شیمی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران تولید سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان انرژی، به‌جز باد و خورشید | مهندسان صنایع | مدیران تولید صنعتی | متصدیان نیروگاه‌های برق | مهندسان تاسیسات و متصدیان دیگ‌های بخار</t>
+          <t>مدیران تولید سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان صنایع | مدیران تولید صنعتی | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | نگارش | علوم | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نگارش | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | ایمنی و امنیت عمومی | مدیریت و امور اداری | مهندسی و فناوری | رایانه و الکترونیک | پرسنلی و منابع انسانی | فیزیک</t>
+          <t>مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره | مهندسی و فناوری | رایانه و الکترونیک | پرسنل و منابع انسانی | فیزیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان برق | مهندسان انرژی، به‌جز باد و خورشید | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران تولید صنعتی | توزیع‌کنندگان و دیسپچرهای برق | متصدیان نیروگاه‌های برق | مهندسان آب و فاضلاب</t>
+          <t>مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | تکنسین‌های نیروگاه برقابی | مدیران تولید صنعتی | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارشناسان لجستیک | تحلیل‌گران لجستیک | کارمندان تدارکات و کارپردازان | کارشناسان خرید، به‌جز محصولات عمده‌فروشی، خرده‌فروشی و کشاورزی | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده و خرده‌فروشی، به‌جز محصولات کشاورزی</t>
+          <t>کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | کارمندان تدارکات و کارپردازی | کارشناسان خرید و امور قراردادها | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | یادگیری فعال | نگارش | سخن گفتن | تفکر انتقادی | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | نگارش | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات | پرسنلی و منابع انسانی | ایمنی و امنیت عمومی | حقوق و مقررات دولتی</t>
+          <t>حمل و نقل | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | قانون و دولت</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان و متصدیان باربری و حمل کالا | دیسپچرهای ترابری، به‌جز پلیس، آتش‌نشانی و اورژانس | فورواردرهای بار و محموله | کارشناسان لجستیک | مدیران خرید و تدارکات | انبارداران، مأموران ورود و خروج و کارمندان کنترل موجودی | مدیران زنجیره تامین</t>
+          <t>کارگزاران حمل‌ونقل و بار | متصدیان دیسپاچ و اعزام | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | کارشناسان لجستیک و مدیریت زنجیره تأمین | مدیران خرید و تدارکات | کارمندان انبار، ارسال و دریافت کالا | مدیران زنجیره تامین</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | مدیریت و امور اداری | اقتصاد و حسابداری | تولید و فرآوری | پرسنلی و منابع انسانی | ریاضیات | رایانه و الکترونیک</t>
+          <t>حمل و نقل | مدیریت و اداره | اقتصاد و حسابداری | تولید و فرآوری | پرسنل و منابع انسانی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان صنایع | کارشناسان لجستیک | تحلیل‌گران لجستیک | کارمندان برنامه‌ریزی تولید، تدارکات و پیگیری | مدیران خرید و تدارکات | انبارداران، مأموران ورود و خروج و کارمندان کنترل موجودی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>مهندسان صنایع | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | مدیران خرید و تدارکات | کارمندان انبار، ارسال و دریافت کالا | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | ریاضیات | حقوق و مقررات دولتی | اداری</t>
+          <t>پرسنل و منابع انسانی | مدیریت و اداره | خدمات مشتری و شخصی | اقتصاد و حسابداری | ریاضیات | قانون و دولت | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تحلیل‌گران بودجه | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارمندان امور پرسنلی و اداری، به‌جز حقوق و دستمزد و حضور و غیاب | مدیران منابع انسانی | کارشناسان منابع انسانی | متصدیان ثبت کارکرد، حضور و غیاب و حقوق و دستمزد</t>
+          <t>حسابداران و حسابرسان | تحلیل‌گران بودجه | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | کارشناسان منابع انسانی | کارمندان امور حقوق، دستمزد و ثبت زمان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و تدریس | حقوق و مقررات دولتی | روان‌شناسی | ارتباطات و رسانه</t>
+          <t>پرسنل و منابع انسانی | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | قانون و دولت | روان‌شناسی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارمندان امور پرسنلی و اداری، به‌جز حقوق و دستمزد و حضور و غیاب | کارشناسان منابع انسانی | کارشناسان روابط کار | مدیران آموزش و بهسازی | کارشناسان آموزش و بهسازی</t>
+          <t>مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | کارشناسان روابط کار و امور تشکل‌های کارگری | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>استراتژی‌های یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | مدیریت و امور اداری | پرسنلی و منابع انسانی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک</t>
+          <t>آموزش و پرورش | مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | ارتباطات و رسانه | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | ابتکار و اصالت</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدرسان آموزش‌های فنی و حرفه‌ای پسامتوسطه | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان سازمانی و صنعتی | هماهنگ‌کنندگان برنامه‌ها و دوره‌های آموزشی | تحلیل‌گران مدیریت | کارشناسان آموزش و بهسازی</t>
+          <t>مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان صنعتی و سازمانی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فرآوری | زیست‌شناسی | پرسنلی و منابع انسانی | صنایع غذایی و تولید خوراک | بازاریابی و فروش | مکانیک</t>
+          <t>مدیریت و اداره | تولید و فرآوری | زیست‌شناسی | پرسنل و منابع انسانی | تولید مواد غذایی | فروش و بازاریابی | مکانیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | متخصصان علوم دامی | کارگران مزارع، پرورش گل و گیاه و گلخانه‌ها | کارگران دامداری، مرغداری و پرورش آبزیان | سرپرستان رده‌اول کارکنان کشاورزی، شیلات و جنگل‌داری | متخصصان علوم خاک و گیاه‌پزشکی</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | متخصصان علوم دامی | کارگران زراعت، نهالستان و گلخانه | کارگران پرورش دام، طیور و آبزیان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | یادگیری فعال | نظارت | نگارش | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ساختمان و سازه | مدیریت و امور اداری | ریاضیات | مهندسی و فناوری | مکانیک | ایمنی و امنیت عمومی | پرسنلی و منابع انسانی</t>
+          <t>ساختمان و ساخت‌وساز | مدیریت و اداره | ریاضیات | مهندسی و فناوری | مکانیک | ایمنی و امنیت عمومی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | تجسم فضایی</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | تکنسین‌ها و کاردان‌های مهندسی عمران | مهندسان عمران | بازرسان ساختمان و سازه | مترورها و برآوردکنندگان هزینه | سرپرستان رده‌اول کارگران ساختمانی و عملیات استخراج | کارشناسان مدیریت پروژه</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | بازرسان ساخت‌وساز و ساختمان | کارشناسان برآورد هزینه و مترورها | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | کارشناسان مدیریت پروژه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
